--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0087.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0087.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Ta sẽ không biến mất. Không phải cho đến khi ta hoàn thành việc này. Đó là lựa chọn của ta.</t>
+          <t>Tao sẽ không biến mất. Không phải cho đến khi tao hoàn thành việc này. Đó là lựa chọn của tao.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ cậu muốn tự mình chứng kiến đến phút cuối.</t>
+          <t>Tao cứ nghĩ cậu muốn tự mình chứng kiến đến phút cuối.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>...Thành phố mà ta yêu quý, người dân nơi đây... tất cả không đáng phải biến mất như thế này.</t>
+          <t>...Thành phố mà tao yêu quý, người dân nơi đây... tất cả không đáng phải biến mất như thế này.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Được rồi. Ta sẽ giúp ngươi.</t>
+          <t>Được rồi. Tao sẽ giúp mày.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Ha! Đúng là cậu nói trúng tim đen ta rồi. Dân Honami mà dính vào thứ gì quan trọng, thì chẳng khác nào con thiêu thân lao vào lửa.</t>
+          <t>Ha! Đúng là cậu nói trúng tim đen tao rồi. Dân Honami mà dính vào thứ gì quan trọng, thì chẳng khác nào con thiêu thân lao vào lửa.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>...Bây giờ, ta còn việc quan trọng hơn phải làm.</t>
+          <t>...Bây giờ, tao còn việc quan trọng hơn phải làm.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Chỉ là... cẩn thận nhé. Ta không muốn ngươi phải vất vả vì ta đâu.</t>
+          <t>Chỉ là... cẩn thận nhé. Tao không muốn mày phải vất vả vì tao đâu.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ta chưa bao giờ nghĩ mình có thể quay lại đây.</t>
+          <t>Tao chưa bao giờ nghĩ mình có thể quay lại đây.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Dù sao với ta cũng vô dụng, vậy thì cầm lấy đi.</t>
+          <t>Dù sao với tao cũng vô dụng, vậy thì cầm lấy đi.</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Cậu nghĩ ai mạnh hơn, Miko-sama hay Sentinel?</t>
+          <t>Mày nghĩ ai mạnh hơn, Miko-sama hay Sentinel?</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Ta sẽ cho ngươi năm triệu phần Bánh Dango nếu ngươi loại được sếp ta!</t>
+          <t>Tao sẽ cho mày năm triệu phần Bánh Dango nếu mày loại được sếp tao!</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Gì? Cậu đã thấy con quái thú đó rồi á? Vậy truyền thuyết là có thật?</t>
+          <t>Gì? Mày đã thấy con quái thú đó rồi á? Vậy truyền thuyết là có thật?</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Ta sẽ đi tìm mẹ cậu. Cậu có biết bà ấy có thể ở đâu không?</t>
+          <t>Tao sẽ đi tìm mẹ cậu. Cậu có biết bà ấy có thể ở đâu không?</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>...! Cảm ơn {Male=cậu;Female=cô}!</t>
+          <t>...! Cảm ơn bạn!</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} ơi, vào lều của em đi.</t>
+          <t>{Male=big brother;Female=big sister} ơi, vào lều của em đi.</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Ta sẽ đi tìm Vantier.</t>
+          <t>Tao sẽ đi tìm Vantier.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Cảm ơn {Male=cậu;Female=cô} đã giúp đỡ mẹ con em nhiều như vậy...</t>
+          <t>Cảm ơn bạn đã giúp đỡ mẹ con em nhiều như vậy...</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Mẫu gì chứ! Sao không nói thẳng là Kronapuff mách cậu? Giờ ăn của tụi nó còn chính xác hơn cái mô hình của cậu!</t>
+          <t>Mẫu gì chứ! Sao không nói thẳng là Kronapuff mách mày? Giờ ăn của tụi nó còn chính xác hơn cái mô hình của mày!</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Iselde à, cậu là trọng tài nhé—Ai đúng đây, ta hay hắn?!</t>
+          <t>Iselde à, cậu là trọng tài nhé—Ai đúng đây, tao hay hắn?!</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Nhưng cũng mấy năm rồi ta mới lại nghe hai đứa cãi nhau. Sao giờ lại dừng vui vậy?</t>
+          <t>Nhưng cũng mấy năm rồi tao mới lại nghe hai đứa cãi nhau. Sao giờ lại dừng vui vậy?</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây?</t>
+          <t>Có chuyện gì mà bạn lại đến đây?</t>
         </is>
       </c>
     </row>
